--- a/Assets/Resources/Old versions/ASKFirstDialogue2Options.xlsx
+++ b/Assets/Resources/Old versions/ASKFirstDialogue2Options.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jayso\ASKFirst v2\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jayso\ASKFirst v2\Assets\Resources\Old versions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA55806F-0F90-4E4F-A0D2-1C3B2387E570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2148ED43-6973-48E2-8951-2B15E2995299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8CF9D31E-0312-48F0-ADC3-94BF3514D222}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8CF9D31E-0312-48F0-ADC3-94BF3514D222}"/>
   </bookViews>
   <sheets>
     <sheet name="ASKFirstDialogue2Options" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16522" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16538" uniqueCount="110">
   <si>
     <t>NPC Name</t>
   </si>
@@ -328,6 +328,30 @@
   </si>
   <si>
     <t>I'll be leaving now…</t>
+  </si>
+  <si>
+    <t>Tutorial</t>
+  </si>
+  <si>
+    <t>Hi! I'm here to teach you how to talk to customers!</t>
+  </si>
+  <si>
+    <t>Are you shoplifting?</t>
+  </si>
+  <si>
+    <t>Pick one of the options below! These are good examples of how to approach customers</t>
+  </si>
+  <si>
+    <t>Great! Look how the mood bar to the left increased? That means you picked a good option!</t>
+  </si>
+  <si>
+    <t>Now pick one of these options! These are bad examples of how to approach customers.</t>
+  </si>
+  <si>
+    <t>See how the mood bar went down instead? That means you picked a bad option</t>
+  </si>
+  <si>
+    <t>That's all you need to know! Remember to follow the ASK Protocols!</t>
   </si>
 </sst>
 </file>
@@ -1281,22 +1305,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60FC667-4F56-45C1-A2CA-D070B5A8D91D}">
-  <dimension ref="A1:XFD58"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:XFD65"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="3" width="15.7265625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="40.7265625" customWidth="1"/>
-    <col min="5" max="5" width="15.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="49.08984375" customWidth="1"/>
-    <col min="7" max="9" width="15.7265625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="40.7265625" customWidth="1"/>
-    <col min="11" max="13" width="15.7265625" style="5" customWidth="1"/>
-    <col min="14" max="22" width="40.7265625" hidden="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.1796875" hidden="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="49.140625" customWidth="1"/>
+    <col min="7" max="9" width="15.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="40.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" style="5" customWidth="1"/>
+    <col min="14" max="22" width="40.7109375" hidden="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1345,7 +1369,7 @@
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1369,7 +1393,7 @@
       <c r="N2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1412,7 +1436,7 @@
       <c r="N3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1436,7 +1460,7 @@
       <c r="N4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1460,7 +1484,7 @@
       <c r="N5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1484,7 +1508,7 @@
       <c r="N6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1511,7 +1535,7 @@
       <c r="N7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="E8" s="19"/>
@@ -1522,7 +1546,7 @@
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
     </row>
-    <row r="9" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -1565,7 +1589,7 @@
       <c r="N9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>48</v>
       </c>
@@ -1589,7 +1613,7 @@
       <c r="N10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>48</v>
       </c>
@@ -1613,7 +1637,7 @@
       <c r="N11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
@@ -1637,7 +1661,7 @@
       <c r="N12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -1680,7 +1704,7 @@
       <c r="N13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -1702,7 +1726,7 @@
       <c r="N14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1724,7 +1748,7 @@
       <c r="N15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
@@ -1746,7 +1770,7 @@
       <c r="N16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1768,7 +1792,7 @@
       <c r="N17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" ht="16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>56</v>
       </c>
@@ -1811,7 +1835,7 @@
       <c r="N18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>56</v>
       </c>
@@ -1854,7 +1878,7 @@
       <c r="N19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>56</v>
       </c>
@@ -1878,7 +1902,7 @@
       <c r="N20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>56</v>
       </c>
@@ -1902,7 +1926,7 @@
       <c r="N21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
@@ -1926,7 +1950,7 @@
       <c r="N22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
       <c r="E23" s="19"/>
@@ -1937,7 +1961,7 @@
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="1:18" ht="32" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:18" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
@@ -1980,7 +2004,7 @@
       <c r="N24" s="1"/>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>73</v>
       </c>
@@ -2002,7 +2026,7 @@
       <c r="N25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>73</v>
       </c>
@@ -2024,7 +2048,7 @@
       <c r="N26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>73</v>
       </c>
@@ -2046,7 +2070,7 @@
       <c r="N27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" ht="16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>82</v>
       </c>
@@ -2089,7 +2113,7 @@
       <c r="N28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
@@ -2111,7 +2135,7 @@
       <c r="N29" s="1"/>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>82</v>
       </c>
@@ -2133,7 +2157,7 @@
       <c r="N30" s="1"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
       <c r="E31" s="19"/>
@@ -2144,7 +2168,7 @@
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>57</v>
       </c>
@@ -2187,7 +2211,7 @@
       <c r="N32" s="1"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>57</v>
       </c>
@@ -2230,7 +2254,7 @@
       <c r="N33" s="1"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>57</v>
       </c>
@@ -2257,7 +2281,7 @@
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
     </row>
-    <row r="35" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>57</v>
       </c>
@@ -2284,7 +2308,7 @@
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
     </row>
-    <row r="36" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>57</v>
       </c>
@@ -2311,7 +2335,7 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
     </row>
-    <row r="37" spans="1:16384" customFormat="1" ht="32" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16384" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>62</v>
       </c>
@@ -2352,7 +2376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>62</v>
       </c>
@@ -2377,7 +2401,7 @@
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
     </row>
-    <row r="39" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>62</v>
       </c>
@@ -2402,7 +2426,7 @@
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
     </row>
-    <row r="40" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>62</v>
       </c>
@@ -2427,7 +2451,7 @@
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
     </row>
-    <row r="41" spans="1:16384" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16384" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -2468,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>72</v>
       </c>
@@ -51606,7 +51630,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>72</v>
       </c>
@@ -51633,7 +51657,7 @@
       <c r="N43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>72</v>
       </c>
@@ -51660,7 +51684,7 @@
       <c r="N44" s="1"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16384" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>72</v>
       </c>
@@ -51687,7 +51711,7 @@
       <c r="N45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:16384" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16384" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
       <c r="E46" s="19"/>
@@ -51698,7 +51722,7 @@
       <c r="L46" s="19"/>
       <c r="M46" s="19"/>
     </row>
-    <row r="47" spans="1:16384" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>91</v>
       </c>
@@ -51741,7 +51765,7 @@
       <c r="N47" s="1"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:16384" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16384" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>91</v>
       </c>
@@ -51784,7 +51808,7 @@
       <c r="N48" s="1"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>91</v>
       </c>
@@ -51808,7 +51832,7 @@
       <c r="N49" s="1"/>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" ht="16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>91</v>
       </c>
@@ -51851,7 +51875,7 @@
       <c r="N50" s="1"/>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>91</v>
       </c>
@@ -51875,7 +51899,7 @@
       <c r="N51" s="1"/>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>91</v>
       </c>
@@ -51899,7 +51923,7 @@
       <c r="N52" s="1"/>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>92</v>
       </c>
@@ -51940,7 +51964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>92</v>
       </c>
@@ -51981,7 +52005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>92</v>
       </c>
@@ -52003,7 +52027,7 @@
       </c>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>92</v>
       </c>
@@ -52023,7 +52047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>92</v>
       </c>
@@ -52043,7 +52067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>92</v>
       </c>
@@ -52060,6 +52084,168 @@
         <v>1</v>
       </c>
       <c r="G58" s="5">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="5">
+        <v>0</v>
+      </c>
+      <c r="C60" s="5">
+        <v>0</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B61" s="5">
+        <v>0</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G61" s="5">
+        <v>2</v>
+      </c>
+      <c r="H61" s="5">
+        <v>4</v>
+      </c>
+      <c r="I61" s="5">
+        <v>-1</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K61" s="5">
+        <v>2</v>
+      </c>
+      <c r="L61" s="5">
+        <v>4</v>
+      </c>
+      <c r="M61" s="5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="5">
+        <v>0</v>
+      </c>
+      <c r="C62" s="5">
+        <v>2</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E62" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" s="5">
+        <v>0</v>
+      </c>
+      <c r="C63" s="5">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" t="s">
+        <v>104</v>
+      </c>
+      <c r="G63" s="5">
+        <v>4</v>
+      </c>
+      <c r="H63" s="5">
+        <v>-4</v>
+      </c>
+      <c r="I63" s="5">
+        <v>-1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" s="5">
+        <v>4</v>
+      </c>
+      <c r="L63" s="5">
+        <v>-4</v>
+      </c>
+      <c r="M63" s="5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B64" s="5">
+        <v>0</v>
+      </c>
+      <c r="C64" s="5">
+        <v>4</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" s="5">
+        <v>0</v>
+      </c>
+      <c r="C65" s="5">
+        <v>5</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5">
         <v>-2</v>
       </c>
     </row>
